--- a/business_forms/042_guest_experience_dashboard_request_form--business_forms.xlsx
+++ b/business_forms/042_guest_experience_dashboard_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'11-1',_'name':_'option1',_'label':_'option_1',_'value':_'option_1_value'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '11-1', 'name': 'option1', 'label': 'Option 1', 'value': 'Option 1 value'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'11-2',_'name':_'option2',_'label':_'option_2',_'value':_'option_2_value'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '11-2', 'name': 'option2', 'label': 'Option 2', 'value': 'Option 2 value'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'11-3',_'name':_'option3',_'label':_'option_3',_'value':_'option_3_value'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '11-3', 'name': 'option3', 'label': 'Option 3', 'value': 'Option 3 value'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'12-1',_'name':_'option11',_'label':_'option_11',_'value':_'option_11_value'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '12-1', 'name': 'option11', 'label': 'Option 11', 'value': 'Option 11 value'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'12-2',_'name':_'option12',_'label':_'option_12',_'value':_'option_12_value'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '12-2', 'name': 'option12', 'label': 'Option 12', 'value': 'Option 12 value'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'12-3',_'name':_'option13',_'label':_'option_13',_'value':_'option_13_value'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '12-3', 'name': 'option13', 'label': 'Option 13', 'value': 'Option 13 value'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
